--- a/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 26,52</t>
+          <t>12,02; 26,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,78; 31,52</t>
+          <t>16,16; 31,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 29,21</t>
+          <t>12,57; 29,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,46</t>
+          <t>0,0; 48,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,69; 28,09</t>
+          <t>13,87; 28,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 25,16</t>
+          <t>10,66; 25,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 29,1</t>
+          <t>12,04; 28,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,7</t>
+          <t>0,0; 35,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,75</t>
+          <t>13,98; 24,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,6; 26,12</t>
+          <t>14,76; 25,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,03; 26,32</t>
+          <t>14,64; 26,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 28,61</t>
+          <t>2,31; 27,29</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 26,03</t>
+          <t>19,47; 26,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,76; 25,19</t>
+          <t>18,83; 25,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,52; 20,4</t>
+          <t>14,6; 20,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 32,64</t>
+          <t>14,77; 32,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,83</t>
+          <t>15,54; 21,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 20,63</t>
+          <t>14,53; 20,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,73; 22,98</t>
+          <t>16,49; 22,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 29,7</t>
+          <t>15,11; 28,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 22,81</t>
+          <t>18,36; 22,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 22,1</t>
+          <t>17,56; 21,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,6; 20,55</t>
+          <t>16,28; 20,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,5; 28,3</t>
+          <t>16,58; 27,69</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,12; 33,34</t>
+          <t>22,36; 33,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 22,87</t>
+          <t>13,06; 22,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 29,68</t>
+          <t>18,5; 29,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 22,32</t>
+          <t>4,2; 21,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,12; 31,43</t>
+          <t>18,94; 30,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,51; 29,52</t>
+          <t>18,9; 29,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,84; 25,37</t>
+          <t>15,51; 25,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 31,38</t>
+          <t>7,55; 30,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,09; 30,29</t>
+          <t>21,86; 30,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 24,97</t>
+          <t>17,08; 24,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 25,37</t>
+          <t>18,03; 25,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 21,77</t>
+          <t>7,91; 22,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,14</t>
+          <t>20,6; 26,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,67</t>
+          <t>18,39; 23,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,45</t>
+          <t>16,56; 21,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 25,97</t>
+          <t>13,49; 26,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,91</t>
+          <t>17,65; 22,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,33</t>
+          <t>16,62; 21,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,21; 22,19</t>
+          <t>17,29; 22,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,95; 25,5</t>
+          <t>13,64; 25,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,84; 23,76</t>
+          <t>20,06; 23,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,15; 21,66</t>
+          <t>18,38; 21,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,03</t>
+          <t>17,53; 21,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,58</t>
+          <t>15,27; 23,54</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12859</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20047</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10834</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13137</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>27845</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33184</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22847</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8583; 18786</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13893; 27283</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6871; 16237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3144</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10268; 21431</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8207; 19829</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7471; 17780</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3340</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20334; 35677</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>24063; 41553</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17088; 30558</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>369; 4360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>84325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>92664</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75479</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15350</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76299</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81464</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84875</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19128</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>160624</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>174129</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>160354</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>34478</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>72483; 98112</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>79257; 107911</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>63254; 89000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9785; 21255</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>63595; 89715</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>67898; 96948</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>72031; 98739</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13792; 26372</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>143510; 177492</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>155928; 193435</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>141657; 179761</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>26116; 43602</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>42455</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27099</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35815</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34555</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38957</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34147</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>77010</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66056</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69961</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8167</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>34498; 51022</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20381; 35800</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28347; 45598</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1157; 6052</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26495; 42680</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31185; 48500</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26520; 43343</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2335; 9301</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>64321; 90698</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>54843; 80086</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>58469; 81949</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4621; 13219</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>139640</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139810</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122128</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19229</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>125839</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>133559</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>25042</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>265479</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>273368</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>253163</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>44271</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>123195; 157361</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>121942; 157901</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106202; 137208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>13530; 26299</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>110039; 142139</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>117878; 152555</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>115814; 147761</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>17947; 33365</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>244973; 289395</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>252276; 301596</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>229916; 277317</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>35401; 54582</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 26,31</t>
+          <t>11,6; 26,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 31,73</t>
+          <t>16,09; 31,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,57; 29,7</t>
+          <t>12,05; 29,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,03</t>
+          <t>0,0; 42,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,94</t>
+          <t>13,75; 28,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,66; 25,76</t>
+          <t>11,38; 25,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 28,65</t>
+          <t>11,81; 28,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,4</t>
+          <t>0,0; 38,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 24,53</t>
+          <t>14,34; 25,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 25,5</t>
+          <t>15,69; 26,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 26,18</t>
+          <t>14,33; 25,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 27,29</t>
+          <t>2,41; 29,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,47; 26,35</t>
+          <t>19,25; 26,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 25,63</t>
+          <t>18,8; 25,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 20,54</t>
+          <t>14,67; 20,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 32,09</t>
+          <t>15,26; 33,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,92</t>
+          <t>15,64; 21,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,53; 20,75</t>
+          <t>14,5; 20,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 22,6</t>
+          <t>16,69; 22,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 28,9</t>
+          <t>14,63; 29,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,71</t>
+          <t>18,28; 22,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 21,78</t>
+          <t>17,5; 21,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 20,66</t>
+          <t>16,37; 20,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 27,69</t>
+          <t>16,79; 27,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,36; 33,07</t>
+          <t>22,41; 33,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 22,94</t>
+          <t>13,11; 23,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 29,76</t>
+          <t>18,28; 29,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 21,98</t>
+          <t>3,48; 21,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,94; 30,5</t>
+          <t>19,69; 30,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 29,39</t>
+          <t>18,36; 28,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,51; 25,34</t>
+          <t>15,1; 25,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 30,09</t>
+          <t>7,54; 30,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,86; 30,83</t>
+          <t>22,29; 30,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 24,94</t>
+          <t>17,11; 24,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 25,27</t>
+          <t>18,1; 25,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 22,62</t>
+          <t>8,45; 22,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 26,31</t>
+          <t>20,62; 26,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 23,81</t>
+          <t>18,41; 23,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,4</t>
+          <t>16,58; 21,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,49; 26,22</t>
+          <t>13,56; 26,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 22,8</t>
+          <t>17,75; 22,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 21,51</t>
+          <t>16,33; 21,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,06</t>
+          <t>16,97; 21,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 25,35</t>
+          <t>14,04; 24,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,06; 23,7</t>
+          <t>19,76; 23,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 21,98</t>
+          <t>18,26; 21,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,53; 21,15</t>
+          <t>17,62; 21,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,27; 23,54</t>
+          <t>14,7; 23,52</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8583; 18786</t>
+          <t>8284; 18723</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13893; 27283</t>
+          <t>13832; 26764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6871; 16237</t>
+          <t>6589; 16293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3144</t>
+          <t>0; 2789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10268; 21431</t>
+          <t>10180; 21381</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8207; 19829</t>
+          <t>8761; 19960</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7471; 17780</t>
+          <t>7331; 17601</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3340</t>
+          <t>0; 3626</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20334; 35677</t>
+          <t>20854; 36490</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24063; 41553</t>
+          <t>25564; 42640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17088; 30558</t>
+          <t>16722; 30253</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>369; 4360</t>
+          <t>385; 4656</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72483; 98112</t>
+          <t>71683; 97320</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79257; 107911</t>
+          <t>79136; 107920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63254; 89000</t>
+          <t>63577; 89416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9785; 21255</t>
+          <t>10110; 21897</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>63595; 89715</t>
+          <t>64034; 89512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67898; 96948</t>
+          <t>67754; 96656</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72031; 98739</t>
+          <t>72889; 99272</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13792; 26372</t>
+          <t>13346; 26908</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>143510; 177492</t>
+          <t>142875; 178633</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>155928; 193435</t>
+          <t>155420; 194499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>141657; 179761</t>
+          <t>142483; 178904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26116; 43602</t>
+          <t>26439; 43903</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34498; 51022</t>
+          <t>34585; 51782</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20381; 35800</t>
+          <t>20464; 36455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28347; 45598</t>
+          <t>28011; 44997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1157; 6052</t>
+          <t>959; 6032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26495; 42680</t>
+          <t>27557; 42668</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31185; 48500</t>
+          <t>30296; 47753</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26520; 43343</t>
+          <t>25824; 43927</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2335; 9301</t>
+          <t>2331; 9297</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64321; 90698</t>
+          <t>65573; 89955</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54843; 80086</t>
+          <t>54956; 78567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58469; 81949</t>
+          <t>58706; 82948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4621; 13219</t>
+          <t>4939; 13372</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123195; 157361</t>
+          <t>123311; 156291</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>121942; 157901</t>
+          <t>122091; 157209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106202; 137208</t>
+          <t>106331; 139069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13530; 26299</t>
+          <t>13605; 26560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110039; 142139</t>
+          <t>110606; 141773</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>117878; 152555</t>
+          <t>115790; 150430</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115814; 147761</t>
+          <t>113675; 147131</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17947; 33365</t>
+          <t>18472; 32847</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244973; 289395</t>
+          <t>241272; 289498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>252276; 301596</t>
+          <t>250582; 298674</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>229916; 277317</t>
+          <t>231019; 277629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35401; 54582</t>
+          <t>34095; 54546</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP18A02-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,06%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,01%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,82%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 26,22</t>
+          <t>13,69; 28,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,09; 31,12</t>
+          <t>10,45; 25,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,05; 29,81</t>
+          <t>11,6; 29,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,62</t>
+          <t>0,0; 35,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 28,87</t>
+          <t>10,96; 26,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 25,93</t>
+          <t>16,78; 31,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 28,36</t>
+          <t>11,8; 29,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,43</t>
+          <t>0,0; 44,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 25,09</t>
+          <t>14,06; 24,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 26,16</t>
+          <t>15,6; 26,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 25,92</t>
+          <t>14,03; 26,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 29,14</t>
+          <t>2,15; 27,23</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>22,65%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>17,42%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,25; 26,14</t>
+          <t>15,47; 21,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 25,63</t>
+          <t>14,66; 20,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,67; 20,63</t>
+          <t>16,73; 22,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 33,06</t>
+          <t>14,7; 30,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 21,87</t>
+          <t>19,38; 26,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 20,69</t>
+          <t>18,76; 25,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 22,73</t>
+          <t>14,52; 20,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 29,49</t>
+          <t>16,02; 35,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,28; 22,85</t>
+          <t>18,38; 22,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 21,9</t>
+          <t>17,68; 22,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 20,56</t>
+          <t>16,6; 20,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,88</t>
+          <t>17,3; 29,69</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27,52%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>23,37%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 33,56</t>
+          <t>19,12; 31,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,11; 23,36</t>
+          <t>18,51; 29,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,28; 29,37</t>
+          <t>15,84; 25,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 21,91</t>
+          <t>8,02; 31,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,69; 30,49</t>
+          <t>22,12; 33,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 28,93</t>
+          <t>12,68; 22,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 25,68</t>
+          <t>18,12; 29,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 30,08</t>
+          <t>4,6; 23,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,29; 30,57</t>
+          <t>22,09; 30,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 24,47</t>
+          <t>17,08; 24,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,58</t>
+          <t>18,09; 25,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 22,88</t>
+          <t>8,24; 22,99</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21,09%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,04%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 26,13</t>
+          <t>17,62; 22,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 23,71</t>
+          <t>16,58; 21,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,58; 21,69</t>
+          <t>17,21; 22,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 26,48</t>
+          <t>14,2; 26,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 22,75</t>
+          <t>20,49; 26,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 21,21</t>
+          <t>18,62; 23,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,97; 21,96</t>
+          <t>16,35; 21,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,96</t>
+          <t>13,93; 27,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 23,7</t>
+          <t>19,84; 23,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 21,77</t>
+          <t>18,15; 21,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 21,17</t>
+          <t>17,69; 21,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,52</t>
+          <t>15,77; 24,6</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13137</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12859</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>20047</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>10834</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13137</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12013</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>853</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>1454</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8284; 18723</t>
+          <t>10140; 20805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13832; 26764</t>
+          <t>8048; 19367</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6589; 16293</t>
+          <t>7201; 18060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2789</t>
+          <t>0; 3200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10180; 21381</t>
+          <t>7824; 18937</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8761; 19960</t>
+          <t>14432; 27103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7331; 17601</t>
+          <t>6448; 15965</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3626</t>
+          <t>0; 2637</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20854; 36490</t>
+          <t>20445; 35999</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25564; 42640</t>
+          <t>25420; 42574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16722; 30253</t>
+          <t>16381; 30724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>385; 4656</t>
+          <t>323; 4096</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76299</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81464</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84875</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18036</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>84325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>92664</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>75479</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15350</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76299</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81464</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84875</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34478</t>
+          <t>33720</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71683; 97320</t>
+          <t>63311; 89353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79136; 107920</t>
+          <t>68489; 96393</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63577; 89416</t>
+          <t>73065; 100377</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10110; 21897</t>
+          <t>12318; 25515</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64034; 89512</t>
+          <t>72175; 96919</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67754; 96656</t>
+          <t>78967; 106049</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72889; 99272</t>
+          <t>62942; 88431</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13346; 26908</t>
+          <t>10131; 22417</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>142875; 178633</t>
+          <t>143687; 178317</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>155420; 194499</t>
+          <t>157039; 196256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>142483; 178904</t>
+          <t>144452; 178785</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26439; 43903</t>
+          <t>25438; 43658</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34555</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38957</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34147</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4928</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>42455</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>27099</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>34555</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38957</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>34147</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>7891</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34585; 51782</t>
+          <t>26748; 43972</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20464; 36455</t>
+          <t>30543; 48726</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28011; 44997</t>
+          <t>27098; 43387</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>959; 6032</t>
+          <t>2311; 9139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27557; 42668</t>
+          <t>34136; 51440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30296; 47753</t>
+          <t>19788; 35688</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25824; 43927</t>
+          <t>27766; 45483</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2331; 9297</t>
+          <t>1211; 6301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65573; 89955</t>
+          <t>64999; 89112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54956; 78567</t>
+          <t>54835; 80189</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58706; 82948</t>
+          <t>58655; 82258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4939; 13372</t>
+          <t>4544; 12681</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125839</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133559</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>131035</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23565</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>139640</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>139810</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>122128</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>125839</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>133559</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>131035</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>43065</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123311; 156291</t>
+          <t>109801; 142771</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122091; 157209</t>
+          <t>117557; 151268</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106331; 139069</t>
+          <t>115286; 148676</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13605; 26560</t>
+          <t>17290; 32281</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110606; 141773</t>
+          <t>122547; 156306</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115790; 150430</t>
+          <t>123450; 156938</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>113675; 147131</t>
+          <t>104847; 137562</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18472; 32847</t>
+          <t>13305; 26436</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>241272; 289498</t>
+          <t>242263; 290219</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>250582; 298674</t>
+          <t>249074; 297172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>231019; 277629</t>
+          <t>231902; 275777</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>34095; 54546</t>
+          <t>34266; 53446</t>
         </is>
       </c>
     </row>
